--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2829,7 +2829,7 @@
         <v>129503676</v>
       </c>
       <c r="B21" t="n">
-        <v>58057</v>
+        <v>58110</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2829,7 +2829,7 @@
         <v>129503676</v>
       </c>
       <c r="B21" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2829,7 +2829,7 @@
         <v>129503676</v>
       </c>
       <c r="B21" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 50817-2025 artfynd.xlsx
+++ b/artfynd/A 50817-2025 artfynd.xlsx
@@ -2829,7 +2829,7 @@
         <v>129503676</v>
       </c>
       <c r="B21" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
